--- a/file/pdd/upload/111.xlsx
+++ b/file/pdd/upload/111.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr updateLinks="always"/>
   <bookViews>
     <workbookView windowHeight="17775"/>
   </bookViews>
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="282">
-  <si>
-    <t>商品ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="630">
+  <si>
+    <t>产品ID</t>
   </si>
   <si>
     <t>红线价格</t>
@@ -38,19 +38,92 @@
     <t>897058144119</t>
   </si>
   <si>
-    <t>大马哈15cm    5.126
-大马哈29cm    8.03
-大马哈41cm    15.95</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大马哈15cm 6.73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大马哈29cm 10.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大马哈41cm 20.94</t>
+    </r>
   </si>
   <si>
     <t>907029242021</t>
   </si>
   <si>
+    <t>925878811134</t>
+  </si>
+  <si>
     <t>897082593662</t>
   </si>
   <si>
-    <t>方块立体祝福10cm    8.162
-方块立体祝福6cm    4.334</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方块立体祝福10cm 10.72</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方块立体祝福6cm 5.69</t>
+    </r>
   </si>
   <si>
     <t>907029216556</t>
@@ -59,8 +132,34 @@
     <t>897088671672</t>
   </si>
   <si>
-    <t>龙马精神关节可动龙35cm    10.329
-龙马精神关节可动龙58cm    51.37</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙马精神关节可动龙35cm 13.56</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙马精神关节可动龙58cm 67.46</t>
+    </r>
   </si>
   <si>
     <t>907029216180</t>
@@ -69,7 +168,7 @@
     <t>897232491873</t>
   </si>
   <si>
-    <t>黑马    8.162</t>
+    <t>黑马 10.72</t>
   </si>
   <si>
     <t>907029288973</t>
@@ -78,16 +177,19 @@
     <t>897255952891</t>
   </si>
   <si>
-    <t>赛博朋克机械手15cm    8.49596</t>
+    <t>赛博朋克机械手15cm 11.16</t>
   </si>
   <si>
     <t>907029134717</t>
   </si>
   <si>
+    <t>926457545219</t>
+  </si>
+  <si>
     <t>897813496861</t>
   </si>
   <si>
-    <t>手榴弹MK2    11.33</t>
+    <t>手榴弹MK2 14.88</t>
   </si>
   <si>
     <t>907029928138</t>
@@ -99,7 +201,7 @@
     <t>897870827177</t>
   </si>
   <si>
-    <t>南极生物    6.71</t>
+    <t>南极生物 8.81</t>
   </si>
   <si>
     <t>907029810569</t>
@@ -108,7 +210,7 @@
     <t>898477855965</t>
   </si>
   <si>
-    <t>KT拼豆漏斗    5.786</t>
+    <t>KT拼豆漏斗 7.6</t>
   </si>
   <si>
     <t>907029337163</t>
@@ -120,10 +222,13 @@
     <t>912314039588</t>
   </si>
   <si>
+    <t>925230506821</t>
+  </si>
+  <si>
     <t>898497569377</t>
   </si>
   <si>
-    <t>忍者星型指尖陀螺    6.88556</t>
+    <t>忍者星型指尖陀螺 9.04</t>
   </si>
   <si>
     <t>907029360522</t>
@@ -132,8 +237,34 @@
     <t>903149250831</t>
   </si>
   <si>
-    <t>寻秦记新版    7.1456
-寻秦记旧版    6.974</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寻秦记新版 9.38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寻秦记旧版 9.16</t>
+    </r>
   </si>
   <si>
     <t>898591125422</t>
@@ -148,7 +279,7 @@
     <t>899645779971</t>
   </si>
   <si>
-    <t>条纹蜥蜴    7.21875</t>
+    <t>条纹蜥蜴 9.48</t>
   </si>
   <si>
     <t>907029881192</t>
@@ -157,7 +288,7 @@
     <t>899648175298</t>
   </si>
   <si>
-    <t>凶狠猫咪    4.7663</t>
+    <t>凶狠猫咪 6.26</t>
   </si>
   <si>
     <t>907029466299</t>
@@ -166,7 +297,7 @@
     <t>899650410824</t>
   </si>
   <si>
-    <t>爱心大眼章鱼    5.8245</t>
+    <t>爱心大眼章鱼 7.65</t>
   </si>
   <si>
     <t>907029156661</t>
@@ -175,9 +306,53 @@
     <t>899651366347</t>
   </si>
   <si>
-    <t>小龙    6.5967
-龙蛋    12.64989
-龙加蛋    16.49659</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小龙 8.66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙蛋 16.61</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>龙加蛋 21.66</t>
+    </r>
   </si>
   <si>
     <t>907029822270</t>
@@ -186,7 +361,7 @@
     <t>899659177176</t>
   </si>
   <si>
-    <t>多色蜘蛛    9.9</t>
+    <t>多色蜘蛛 13</t>
   </si>
   <si>
     <t>907029596135</t>
@@ -195,7 +370,7 @@
     <t>899665522815</t>
   </si>
   <si>
-    <t>方块毛毛虫    7.04</t>
+    <t>方块毛毛虫 9.24</t>
   </si>
   <si>
     <t>907029274993</t>
@@ -204,7 +379,7 @@
     <t>899669052018</t>
   </si>
   <si>
-    <t>爱心龙    9.185</t>
+    <t>爱心龙 12.06</t>
   </si>
   <si>
     <t>907029465487</t>
@@ -213,7 +388,7 @@
     <t>899672239782</t>
   </si>
   <si>
-    <t>拼装小马    9.9</t>
+    <t>拼装小马 13</t>
   </si>
   <si>
     <t>907029369901</t>
@@ -222,7 +397,7 @@
     <t>899700890926</t>
   </si>
   <si>
-    <t>米菲兔豆铲    5.8718</t>
+    <t>米菲兔豆铲 7.71</t>
   </si>
   <si>
     <t>907029120425</t>
@@ -231,7 +406,7 @@
     <t>900088619943</t>
   </si>
   <si>
-    <t>双色kt双针豆笔    3.6795</t>
+    <t>双色kt双针豆笔 4.83</t>
   </si>
   <si>
     <t>907014421740</t>
@@ -240,11 +415,40 @@
     <t>911794524968</t>
   </si>
   <si>
+    <t>926463335443</t>
+  </si>
+  <si>
     <t>900090466348</t>
   </si>
   <si>
-    <t>麦当劳豆铲(小)    6.6176
-麦当劳豆铲(大)    9.2576</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>麦当劳豆铲(小) 8.69</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>麦当劳豆铲(大) 12.16</t>
+    </r>
   </si>
   <si>
     <t>907029014698</t>
@@ -253,7 +457,7 @@
     <t>900204339606</t>
   </si>
   <si>
-    <t>复活节兔子蛋螺旋蛋    5.48636</t>
+    <t>复活节兔子蛋螺旋蛋 7.2</t>
   </si>
   <si>
     <t>907029072076</t>
@@ -262,7 +466,7 @@
     <t>900205322493</t>
   </si>
   <si>
-    <t>复活节兔子蛋烟花蛋    9.8516</t>
+    <t>复活节兔子蛋烟花蛋 12.94</t>
   </si>
   <si>
     <t>907029808595</t>
@@ -271,7 +475,7 @@
     <t>900208597423</t>
   </si>
   <si>
-    <t>复活节兔子蛋竖纹蛋    9.97304</t>
+    <t>复活节兔子蛋竖纹蛋 13.1</t>
   </si>
   <si>
     <t>907029262443</t>
@@ -280,7 +484,7 @@
     <t>900219161043</t>
   </si>
   <si>
-    <t>复活节兔子蛋向日葵蛋    10.769</t>
+    <t>复活节兔子蛋向日葵蛋 14.14</t>
   </si>
   <si>
     <t>907029037326</t>
@@ -289,7 +493,7 @@
     <t>900250230214</t>
   </si>
   <si>
-    <t>复活节兔子蛋镂空蛋    9.41336</t>
+    <t>复活节兔子蛋镂空蛋 12.36</t>
   </si>
   <si>
     <t>907029535664</t>
@@ -298,10 +502,72 @@
     <t>900258209115</t>
   </si>
   <si>
-    <t>深海迷航海龙利维坦    12.254
-深海迷航冰虫利维坦    12.73976
-深海迷航潜行者    5.7332
-深海迷航臭臭鱼    7.2908</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深海迷航海龙利维坦 16.09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深海迷航冰虫利维坦 16.73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深海迷航潜行者 7.53</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深海迷航臭臭鱼 9.57</t>
+    </r>
   </si>
   <si>
     <t>907028989687</t>
@@ -313,7 +579,7 @@
     <t>900737858141</t>
   </si>
   <si>
-    <t>马头拖车头球盖    7.1984</t>
+    <t>马头拖车头球盖 9.45</t>
   </si>
   <si>
     <t>907029048567</t>
@@ -322,7 +588,7 @@
     <t>900735713153</t>
   </si>
   <si>
-    <t>2胡须kt双针豆夹    3.806</t>
+    <t>2胡须kt双针豆夹 5</t>
   </si>
   <si>
     <t>907012488347</t>
@@ -331,8 +597,34 @@
     <t>900717816511</t>
   </si>
   <si>
-    <t>海龙34cm    8.954
-海龙49cm    17.27</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海龙34cm 11.76</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海龙49cm 22.68</t>
+    </r>
   </si>
   <si>
     <t>907029297732</t>
@@ -341,7 +633,7 @@
     <t>900821127783</t>
   </si>
   <si>
-    <t>跳跳马    8.558</t>
+    <t>跳跳马 11.24</t>
   </si>
   <si>
     <t>907029676982</t>
@@ -350,7 +642,7 @@
     <t>900846517330</t>
   </si>
   <si>
-    <t>可爱小马驹    8.558</t>
+    <t>可爱小马驹 11.24</t>
   </si>
   <si>
     <t>907029261389</t>
@@ -359,14 +651,148 @@
     <t>900853405442</t>
   </si>
   <si>
-    <t>元宝小马系列招财坐款抱元宝    6.64675
-元宝小马系列招财踏福迎财    5.430535
-元宝小马系列童趣招财摇摇马    6.02041
-元宝小马系列稳步招财漫步驮宝    7.213602
-元宝小马系列祥瑞独角福运    5.29254
-元宝小马系列励志飞黄腾达    6.23348
-元宝小马系列可爱圆滚滚福气    4.31728
-元宝小马系列旺运驮币铜钱    6.27781</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列招财坐款抱元宝 8.73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列招财踏福迎财 7.13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列童趣招财摇摇马 7.91</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列稳步招财漫步驮宝 9.47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列祥瑞独角福运 6.95</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列励志飞黄腾达 8.19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列可爱圆滚滚福气 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>元宝小马系列旺运驮币铜钱 8.24</t>
+    </r>
   </si>
   <si>
     <t>907029546786</t>
@@ -375,7 +801,7 @@
     <t>900928405431</t>
   </si>
   <si>
-    <t>三角洲蝴蝶刀影锋    6.71</t>
+    <t>三角洲蝴蝶刀影锋 8.81</t>
   </si>
   <si>
     <t>907029487128</t>
@@ -384,7 +810,7 @@
     <t>901389694421</t>
   </si>
   <si>
-    <t>绳结卡    7.04</t>
+    <t>绳结卡 9.24</t>
   </si>
   <si>
     <t>907029593446</t>
@@ -393,7 +819,7 @@
     <t>907528159842</t>
   </si>
   <si>
-    <t>我的世界小猫    3.8225</t>
+    <t>我的世界小猫 5.02</t>
   </si>
   <si>
     <t>901436582204</t>
@@ -408,18 +834,185 @@
     <t>911760634644</t>
   </si>
   <si>
+    <t>925754150042</t>
+  </si>
+  <si>
+    <t>926562489265</t>
+  </si>
+  <si>
+    <t>925893026663</t>
+  </si>
+  <si>
+    <t>931298528638</t>
+  </si>
+  <si>
+    <t>931376671770</t>
+  </si>
+  <si>
     <t>901462500400</t>
   </si>
   <si>
-    <t>对联冰箱贴平安喜乐    7.78646
-对联冰箱贴财富加马    5.57139
-对联冰箱贴马年大🍊    7.84652
-冰箱贴2026马    3.608
-冰箱贴马上有钱    4.1085
-冰箱贴马到成功    4.35017
-冰箱贴立马转运    4.34302
-冰箱贴大马    7.04
-冰箱贴福    7.04</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对联冰箱贴平安喜乐 10.22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对联冰箱贴财富加马 7.32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对联冰箱贴马年大🍊 10.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冰箱贴2026马 4.74</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冰箱贴马上有钱 5.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冰箱贴马到成功 5.71</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冰箱贴立马转运 5.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冰箱贴大马 9.24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冰箱贴福 9.24</t>
+    </r>
   </si>
   <si>
     <t>907029760671</t>
@@ -428,7 +1021,7 @@
     <t>901811590441</t>
   </si>
   <si>
-    <t>三角洲刀片服务器    10.89</t>
+    <t>三角洲刀片服务器 14.3</t>
   </si>
   <si>
     <t>907011147751</t>
@@ -437,10 +1030,43 @@
     <t>909364304892</t>
   </si>
   <si>
+    <t>925860155272</t>
+  </si>
+  <si>
+    <t>930016401897</t>
+  </si>
+  <si>
+    <t>930018423890</t>
+  </si>
+  <si>
+    <t>930020407621</t>
+  </si>
+  <si>
+    <t>930018969545</t>
+  </si>
+  <si>
+    <t>930478532041</t>
+  </si>
+  <si>
+    <t>930478450633</t>
+  </si>
+  <si>
+    <t>930481301465</t>
+  </si>
+  <si>
+    <t>930618202693</t>
+  </si>
+  <si>
+    <t>931288063508</t>
+  </si>
+  <si>
+    <t>931278137532</t>
+  </si>
+  <si>
     <t>902306151863</t>
   </si>
   <si>
-    <t>四色金箍棒    21.95996</t>
+    <t>四色金箍棒 28.84</t>
   </si>
   <si>
     <t>907029735406</t>
@@ -449,13 +1075,31 @@
     <t>902320990789</t>
   </si>
   <si>
-    <t>无畏契约爪子刀    6.05</t>
+    <t>无畏契约爪子刀 7.94</t>
+  </si>
+  <si>
+    <t>925219716644</t>
+  </si>
+  <si>
+    <t>925936965394</t>
+  </si>
+  <si>
+    <t>925904813774</t>
+  </si>
+  <si>
+    <t>907014772708</t>
+  </si>
+  <si>
+    <t>931378314665</t>
+  </si>
+  <si>
+    <t>931380743570</t>
   </si>
   <si>
     <t>903037756964</t>
   </si>
   <si>
-    <t>机甲浪人哨兵雕像    6.05</t>
+    <t>机甲浪人哨兵雕像 7.94</t>
   </si>
   <si>
     <t>907029379496</t>
@@ -464,7 +1108,7 @@
     <t>903033856423</t>
   </si>
   <si>
-    <t>超梦骨骼宝可梦    6.314</t>
+    <t>超梦骨骼宝可梦 8.29</t>
   </si>
   <si>
     <t>907029498022</t>
@@ -473,7 +1117,7 @@
     <t>903096456435</t>
   </si>
   <si>
-    <t>我的世界龙蛋    6.754</t>
+    <t>我的世界龙蛋 8.87</t>
   </si>
   <si>
     <t>907029069522</t>
@@ -482,7 +1126,7 @@
     <t>903089728507</t>
   </si>
   <si>
-    <t>暴鲤龙骨骼宝可梦    6.7298</t>
+    <t>暴鲤龙骨骼宝可梦 8.84</t>
   </si>
   <si>
     <t>907028977445</t>
@@ -491,7 +1135,7 @@
     <t>903150661406</t>
   </si>
   <si>
-    <t>菠萝章鱼手雷    8.756</t>
+    <t>菠萝章鱼手雷 11.5</t>
   </si>
   <si>
     <t>907028929087</t>
@@ -500,8 +1144,34 @@
     <t>903366679461</t>
   </si>
   <si>
-    <t>三角洲金图纸普通版    4.9665
-三角洲金图纸完美复刻版    6.5395</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三角洲金图纸普通版 6.52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三角洲金图纸完美复刻版 8.59</t>
+    </r>
   </si>
   <si>
     <t>903366002339</t>
@@ -519,8 +1189,34 @@
     <t>903741820033</t>
   </si>
   <si>
-    <t>阿凡达斑溪兽飞行翼龙大    17.325
-阿凡达斑溪兽飞行翼龙大底座    6.05</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阿凡达斑溪兽飞行翼龙大 22.75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阿凡达斑溪兽飞行翼龙大底座 7.94</t>
+    </r>
   </si>
   <si>
     <t>907029248106</t>
@@ -529,9 +1225,53 @@
     <t>903454747958</t>
   </si>
   <si>
-    <t>月亮来了不带环绒毛表面    9.35
-月亮来了不带环光滑表面    12.65
-月亮来了带环光滑表面    17.93</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月亮来了不带环绒毛表面 12.28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月亮来了不带环光滑表面 16.61</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月亮来了带环光滑表面 23.54</t>
+    </r>
   </si>
   <si>
     <t>906605455128</t>
@@ -543,7 +1283,7 @@
     <t>904094932367</t>
   </si>
   <si>
-    <t>王权富贵发冠    6.182</t>
+    <t>王权富贵发冠 8.12</t>
   </si>
   <si>
     <t>907029472680</t>
@@ -552,7 +1292,7 @@
     <t>904361506882</t>
   </si>
   <si>
-    <t>以德服人 以德斧人 斧子    9.086</t>
+    <t>以德服人 以德斧人 斧子 11.93</t>
   </si>
   <si>
     <t>907028714348</t>
@@ -561,10 +1301,40 @@
     <t>910867614472</t>
   </si>
   <si>
+    <t>926469159359</t>
+  </si>
+  <si>
+    <t>931402284574</t>
+  </si>
+  <si>
+    <t>931802693667</t>
+  </si>
+  <si>
     <t>907029496599</t>
   </si>
   <si>
-    <t>三角洲量子储存    4.1558</t>
+    <t>三角洲量子储存 5.46</t>
+  </si>
+  <si>
+    <t>922971110572</t>
+  </si>
+  <si>
+    <t>926512449829</t>
+  </si>
+  <si>
+    <t>926453779898</t>
+  </si>
+  <si>
+    <t>931386321991</t>
+  </si>
+  <si>
+    <t>931388732481</t>
+  </si>
+  <si>
+    <t>922972316253</t>
+  </si>
+  <si>
+    <t>三角洲海盗金币 5.52</t>
   </si>
   <si>
     <t>907028904397</t>
@@ -573,7 +1343,7 @@
     <t>904608571345</t>
   </si>
   <si>
-    <t>三角洲信条粉色30cm    20.4776</t>
+    <t>三角洲信条粉色30cm 26.89</t>
   </si>
   <si>
     <t>907029330249</t>
@@ -585,17 +1355,52 @@
     <t>905050011734</t>
   </si>
   <si>
-    <t>刻律德菈棋子国王蓝    9.218
-刻律德菈棋子王后金    7.238</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刻律德菈棋子国王蓝 12.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刻律德菈棋子王后金 9.5</t>
+    </r>
   </si>
   <si>
     <t>907029378116</t>
   </si>
   <si>
+    <t>925929808230</t>
+  </si>
+  <si>
+    <t>931382397270</t>
+  </si>
+  <si>
+    <t>931385201965</t>
+  </si>
+  <si>
     <t>905032516836</t>
   </si>
   <si>
-    <t>超级马里奥骨架    7.11656</t>
+    <t>超级马里奥骨架 9.34</t>
   </si>
   <si>
     <t>907028986856</t>
@@ -604,16 +1409,19 @@
     <t>905349427645</t>
   </si>
   <si>
-    <t>换挡解压玩具 V2 - 齿轮换挡    9.54811</t>
+    <t>换挡解压玩具 V2 - 齿轮换挡 12.54</t>
   </si>
   <si>
     <t>907029544438</t>
   </si>
   <si>
+    <t>925957016088</t>
+  </si>
+  <si>
     <t>906425066615</t>
   </si>
   <si>
-    <t>一个亿 小目标    12.76</t>
+    <t>一个亿 小目标 16.76</t>
   </si>
   <si>
     <t>907029354699</t>
@@ -622,30 +1430,222 @@
     <t>907083260921</t>
   </si>
   <si>
-    <t>海洋动物水龙    10.615
-海洋动物蛇颈龙    12.386
-海洋动物大鲸鱼    10.615
-海洋动物大嘴鲨鱼    8.91044
-海洋动物红嘴大嘴鲨鱼    8.91044</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海洋动物水龙 13.94</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海洋动物蛇颈龙 16.26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海洋动物大鲸鱼 13.94</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海洋动物大嘴鲨鱼 11.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海洋动物红嘴大嘴鲨鱼 11.7</t>
+    </r>
   </si>
   <si>
     <t>907092422252</t>
   </si>
   <si>
-    <t>海洋动物大嘴鲨鱼    8.91044
-海洋动物红嘴大嘴鲨鱼    8.91044</t>
-  </si>
-  <si>
     <t>908654566735</t>
   </si>
   <si>
-    <t>黏土小人绿色    4.4396
-黏土小人橙色    4.4396
-黏土小人浅蓝色    4.2284
-黏土小人粉色    4.598
-黏土小人深蓝色    4.994
-黏土小人灰色    4.07
-黏土小人六件套    13.0196</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黏土小人绿色 5.83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黏土小人橙色 5.83</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黏土小人浅蓝色 5.55</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黏土小人粉色 6.04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黏土小人深蓝色 6.56</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黏土小人灰色 5.34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>黏土小人六件套 17.1</t>
+    </r>
   </si>
   <si>
     <t>910995472702</t>
@@ -654,25 +1654,141 @@
     <t>908814536252</t>
   </si>
   <si>
-    <t>多色小美人鱼    4.51605</t>
+    <t>多色小美人鱼 5.93</t>
   </si>
   <si>
     <t>908848832088</t>
   </si>
   <si>
-    <t>气球狗    4.532</t>
+    <t>气球狗 5.95</t>
   </si>
   <si>
     <t>909527595807</t>
   </si>
   <si>
-    <t>苹果拼豆笔    3.806
-桃子拼豆笔    3.806
-菠萝拼豆笔    4.07
-葡萄拼豆笔    3.9116
-西瓜拼豆笔    3.9116
-梨子拼豆笔    3.7268
-水果系列全套拼豆笔    9.482</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>苹果拼豆笔 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>桃子拼豆笔 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菠萝拼豆笔 5.34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>葡萄拼豆笔 5.14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>西瓜拼豆笔 5.14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>梨子拼豆笔 4.89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水果系列全套拼豆笔 12.45</t>
+    </r>
   </si>
   <si>
     <t>910995269673</t>
@@ -684,7 +1800,7 @@
     <t>910892877885</t>
   </si>
   <si>
-    <t>幻彩流光马头摆件    4.862</t>
+    <t>幻彩流光马头摆件 6.38</t>
   </si>
   <si>
     <t>910994654668</t>
@@ -693,7 +1809,7 @@
     <t>909580849368</t>
   </si>
   <si>
-    <t>手机握把    4.6772</t>
+    <t>手机握把 6.14</t>
   </si>
   <si>
     <t>910995292702</t>
@@ -702,10 +1818,19 @@
     <t>911034162673</t>
   </si>
   <si>
+    <t>922508977035</t>
+  </si>
+  <si>
+    <t>925019466973</t>
+  </si>
+  <si>
+    <t>926489080444</t>
+  </si>
+  <si>
     <t>910999856422</t>
   </si>
   <si>
-    <t>鹰哨    4.334</t>
+    <t>鹰哨 5.69</t>
   </si>
   <si>
     <t>911740728942</t>
@@ -714,7 +1839,7 @@
     <t>910993471752</t>
   </si>
   <si>
-    <t>糖果笔筒    6.05</t>
+    <t>糖果笔筒 7.94</t>
   </si>
   <si>
     <t>911006216743</t>
@@ -723,14 +1848,40 @@
     <t>913151683317</t>
   </si>
   <si>
-    <t>我的世界恶魂大    6.611
-我的世界恶魂小    3.751</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我的世界恶魂大 8.68</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我的世界恶魂小 4.93</t>
+    </r>
   </si>
   <si>
     <t>913740661903</t>
   </si>
   <si>
-    <t>扭扭解压龙蛋    13.97</t>
+    <t>扭扭解压龙蛋 18.34</t>
   </si>
   <si>
     <t>913829645903</t>
@@ -739,7 +1890,7 @@
     <t>913759792642</t>
   </si>
   <si>
-    <t>扭扭高尔夫球    11.0396</t>
+    <t>扭扭高尔夫球 14.5</t>
   </si>
   <si>
     <t>913771438728</t>
@@ -748,7 +1899,7 @@
     <t>913797299017</t>
   </si>
   <si>
-    <t>兔子蛋    5.2976</t>
+    <t>兔子蛋 6.96</t>
   </si>
   <si>
     <t>913812015529</t>
@@ -757,7 +1908,7 @@
     <t>913824250774</t>
   </si>
   <si>
-    <t>霉豆腐    12.386</t>
+    <t>霉豆腐 16.26</t>
   </si>
   <si>
     <t>914439364609</t>
@@ -766,8 +1917,34 @@
     <t>914401826082</t>
   </si>
   <si>
-    <t>新月亮5cm    4.51616
-新月亮8cm    8.10392</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新月亮5cm 5.93</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新月亮8cm 10.64</t>
+    </r>
   </si>
   <si>
     <t>914382574896</t>
@@ -776,10 +1953,13 @@
     <t>914456949763</t>
   </si>
   <si>
+    <t>925764973339</t>
+  </si>
+  <si>
     <t>915846452195</t>
   </si>
   <si>
-    <t>超大发卡    5.8388</t>
+    <t>超大发卡 7.67</t>
   </si>
   <si>
     <t>915773511467</t>
@@ -788,7 +1968,7 @@
     <t>916418796387</t>
   </si>
   <si>
-    <t>指环王圣盔谷    8.162</t>
+    <t>指环王圣盔谷 10.72</t>
   </si>
   <si>
     <t>916411704569</t>
@@ -797,26 +1977,52 @@
     <t>916410134467</t>
   </si>
   <si>
-    <t>健身兄弟猫    5.43125</t>
+    <t>健身兄弟猫 7.13</t>
   </si>
   <si>
     <t>916993179488</t>
   </si>
   <si>
-    <t>圣帕特里克小黄鸭    5.65576</t>
+    <t>圣帕特里克小黄鸭 7.43</t>
   </si>
   <si>
     <t>916420055919</t>
   </si>
   <si>
-    <t>独角兽鸭子5cm    5.24678</t>
+    <t>独角兽鸭子5cm 6.89</t>
   </si>
   <si>
     <t>916879203296</t>
   </si>
   <si>
-    <t>可爱小蜜蜂    3.1075
-蜜蜂盒子    12.122</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可爱小蜜蜂 4.08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蜜蜂盒子 15.92</t>
+    </r>
   </si>
   <si>
     <t>916890987436</t>
@@ -828,7 +2034,7 @@
     <t>917023665416</t>
   </si>
   <si>
-    <t>小浣熊    4.98795</t>
+    <t>小浣熊 6.55</t>
   </si>
   <si>
     <t>917033101019</t>
@@ -837,7 +2043,7 @@
     <t>917683774787</t>
   </si>
   <si>
-    <t>魔鬼鱼    7.3546</t>
+    <t>魔鬼鱼 9.66</t>
   </si>
   <si>
     <t>917711998593</t>
@@ -846,23 +2052,103 @@
     <t>917681985630</t>
   </si>
   <si>
-    <t>大猩猩    5.9675</t>
+    <t>大猩猩 7.84</t>
   </si>
   <si>
     <t>917651332468</t>
   </si>
   <si>
-    <t>海绵宝宝雕像    9.21008
-派大星雕像    9.812
-章鱼哥雕像    8.83784
-蟹老板雕像    9.62852
-痞老板雕像    9.37112</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>海绵宝宝雕像 12.09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>派大星雕像 12.88</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>章鱼哥雕像 11.61</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蟹老板雕像 12.64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>痞老板雕像 12.31</t>
+    </r>
   </si>
   <si>
     <t>917700328777</t>
   </si>
   <si>
-    <t>球类解压萝卜    9.35</t>
+    <t>球类解压萝卜 12.28</t>
   </si>
   <si>
     <t>917659869694</t>
@@ -871,8 +2157,34 @@
     <t>917695402638</t>
   </si>
   <si>
-    <t>RTX5090    5.82428
-RTX4090    6.897</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>RTX5090 7.65</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>RTX4090 9.06</t>
+    </r>
   </si>
   <si>
     <t>917728643993</t>
@@ -881,22 +2193,25 @@
     <t>918971092761</t>
   </si>
   <si>
-    <t>玫瑰乌龟    4.895</t>
+    <t>玫瑰乌龟 6.43</t>
   </si>
   <si>
     <t>920276936664</t>
   </si>
   <si>
-    <t>我的世界小床8cm    6.314</t>
+    <t>我的世界小床8cm 8.29</t>
   </si>
   <si>
     <t>918261592451</t>
   </si>
   <si>
+    <t>921013789915</t>
+  </si>
+  <si>
     <t>918977034229</t>
   </si>
   <si>
-    <t>蝴蝶龙    5.23534</t>
+    <t>蝴蝶龙 6.87</t>
   </si>
   <si>
     <t>919014041184</t>
@@ -905,7 +2220,7 @@
     <t>919029294038</t>
   </si>
   <si>
-    <t>扭扭中空滚筒按摩棒    10.0826</t>
+    <t>扭扭中空滚筒按摩棒 13.24</t>
   </si>
   <si>
     <t>919043008949</t>
@@ -914,22 +2229,1888 @@
     <t>920229727537</t>
   </si>
   <si>
-    <t>玫瑰龙    6.3822</t>
+    <t>玫瑰龙 8.38</t>
   </si>
   <si>
     <t>920294245800</t>
   </si>
   <si>
-    <t>郁金香龙    5.522</t>
+    <t>郁金香龙 7.25</t>
+  </si>
+  <si>
+    <t>921026778073</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>轮胎笔筒绿色大 13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>轮胎笔筒蓝色大 13.38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>轮胎笔筒红色大 12.25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>轮胎笔筒绿色小 9.24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>轮胎笔筒蓝色小 9.43</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>轮胎笔筒红色小 8.87</t>
+    </r>
+  </si>
+  <si>
+    <t>920947695628</t>
   </si>
   <si>
     <t>918994068398</t>
   </si>
   <si>
-    <t>随机拼豆笔    4.07</t>
+    <t>随机拼豆笔 5.34</t>
   </si>
   <si>
     <t>918974034216</t>
+  </si>
+  <si>
+    <t>921653663028</t>
+  </si>
+  <si>
+    <t>针织纹理解压旋转指尖陀螺 6.99</t>
+  </si>
+  <si>
+    <t>921723206314</t>
+  </si>
+  <si>
+    <t>921711407868</t>
+  </si>
+  <si>
+    <t>921669015888</t>
+  </si>
+  <si>
+    <t>粉色尖角龙 8.49</t>
+  </si>
+  <si>
+    <t>921753663461</t>
+  </si>
+  <si>
+    <t>921671437996</t>
+  </si>
+  <si>
+    <t>尖角蜥蜴 7.94</t>
+  </si>
+  <si>
+    <t>922411561653</t>
+  </si>
+  <si>
+    <t>指尖陀螺旋转菜刀 9.96</t>
+  </si>
+  <si>
+    <t>923001938393</t>
+  </si>
+  <si>
+    <t>923214443096</t>
+  </si>
+  <si>
+    <t>922380599497</t>
+  </si>
+  <si>
+    <t>三角洲大红马上转运 8.8</t>
+  </si>
+  <si>
+    <t>922992160023</t>
+  </si>
+  <si>
+    <t>927344282877</t>
+  </si>
+  <si>
+    <t>927334140294</t>
+  </si>
+  <si>
+    <t>927350507322</t>
+  </si>
+  <si>
+    <t>927351978257</t>
+  </si>
+  <si>
+    <t>931868114953</t>
+  </si>
+  <si>
+    <t>931865022876</t>
+  </si>
+  <si>
+    <t>923191069223</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吃豆人带按键 6.73</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吃豆人幽灵带按键 7.34</t>
+    </r>
+  </si>
+  <si>
+    <t>923104788376</t>
+  </si>
+  <si>
+    <t>923117572852</t>
+  </si>
+  <si>
+    <t>927377390574</t>
+  </si>
+  <si>
+    <t>927367375590</t>
+  </si>
+  <si>
+    <t>927363318462</t>
+  </si>
+  <si>
+    <t>927357757151</t>
+  </si>
+  <si>
+    <t>923009180668</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>苹果派摆件款 8.52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>苹果派钥匙扣款 9.08</t>
+    </r>
+  </si>
+  <si>
+    <t>923205119695</t>
+  </si>
+  <si>
+    <t>923094170254</t>
+  </si>
+  <si>
+    <t>苹果派摆件款 8.52</t>
+  </si>
+  <si>
+    <t>923853569021</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三角洲金刚防弹衣 10.28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三角洲重型头盔 6.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三角洲金刚防弹衣支架底座 10.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三角洲金刚防弹衣加头盔全套 19.3</t>
+    </r>
+  </si>
+  <si>
+    <t>923857521865</t>
+  </si>
+  <si>
+    <t>解压陀螺飞镖 5.94</t>
+  </si>
+  <si>
+    <t>923889345604</t>
+  </si>
+  <si>
+    <t>923849735565</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方块马13cm 6.21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方块马16.5cm 7.91</t>
+    </r>
+  </si>
+  <si>
+    <t>923882189519</t>
+  </si>
+  <si>
+    <t>924989186461</t>
+  </si>
+  <si>
+    <t>月亮滑动翻转块 5.23</t>
+  </si>
+  <si>
+    <t>923810026763</t>
+  </si>
+  <si>
+    <t>924998803445</t>
+  </si>
+  <si>
+    <t>925191117266</t>
+  </si>
+  <si>
+    <t>骏马笔筒 9.52</t>
+  </si>
+  <si>
+    <t>925209439350</t>
+  </si>
+  <si>
+    <t>925187674030</t>
+  </si>
+  <si>
+    <t>摇摇弹簧马 10.11</t>
+  </si>
+  <si>
+    <t>925210289464</t>
+  </si>
+  <si>
+    <t>925189876221</t>
+  </si>
+  <si>
+    <t>925241615114</t>
+  </si>
+  <si>
+    <t>指尖陀螺飞镖(闪电) 5.49</t>
+  </si>
+  <si>
+    <t>927129577329</t>
+  </si>
+  <si>
+    <t>926704713665</t>
+  </si>
+  <si>
+    <t>926699398510</t>
+  </si>
+  <si>
+    <t>926690662115</t>
+  </si>
+  <si>
+    <t>927161097471</t>
+  </si>
+  <si>
+    <t>926704216633</t>
+  </si>
+  <si>
+    <t>926701281310</t>
+  </si>
+  <si>
+    <t>926690539265</t>
+  </si>
+  <si>
+    <t>926478167162</t>
+  </si>
+  <si>
+    <t>羽绒服笔筒 12.47</t>
+  </si>
+  <si>
+    <t>926561405279</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我的刀盾多色 10.92</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我的刀盾单色 9.01</t>
+    </r>
+  </si>
+  <si>
+    <t>926679863892</t>
+  </si>
+  <si>
+    <t>926685314202</t>
+  </si>
+  <si>
+    <t>我的刀盾多色 10.92</t>
+  </si>
+  <si>
+    <t>927128013396</t>
+  </si>
+  <si>
+    <t>926678626291</t>
+  </si>
+  <si>
+    <t>926683313500</t>
+  </si>
+  <si>
+    <t>927164278405</t>
+  </si>
+  <si>
+    <t>926688039930</t>
+  </si>
+  <si>
+    <t>我的刀盾单色 9.01</t>
+  </si>
+  <si>
+    <t>926686299797</t>
+  </si>
+  <si>
+    <t>926579018315</t>
+  </si>
+  <si>
+    <t>咒术回战中秤金次的锤子 21.57</t>
+  </si>
+  <si>
+    <t>926650599101</t>
+  </si>
+  <si>
+    <t>926656527014</t>
+  </si>
+  <si>
+    <t>926659897540</t>
+  </si>
+  <si>
+    <t>926677423251</t>
+  </si>
+  <si>
+    <t>926649828598</t>
+  </si>
+  <si>
+    <t>926658820346</t>
+  </si>
+  <si>
+    <t>926676075940</t>
+  </si>
+  <si>
+    <t>926678280852</t>
+  </si>
+  <si>
+    <t>927286679311</t>
+  </si>
+  <si>
+    <t>趴玻璃的皮卡丘 14.36</t>
+  </si>
+  <si>
+    <t>927290270476</t>
+  </si>
+  <si>
+    <t>927295061790</t>
+  </si>
+  <si>
+    <t>927300573793</t>
+  </si>
+  <si>
+    <t>927303764242</t>
+  </si>
+  <si>
+    <t>927308154995</t>
+  </si>
+  <si>
+    <t>927287500329</t>
+  </si>
+  <si>
+    <t>927275186440</t>
+  </si>
+  <si>
+    <t>927270522753</t>
+  </si>
+  <si>
+    <t>927265307013</t>
+  </si>
+  <si>
+    <t>931998724216</t>
+  </si>
+  <si>
+    <t>931975423607</t>
+  </si>
+  <si>
+    <t>927292622058</t>
+  </si>
+  <si>
+    <t>旋转飞镖 6.21</t>
+  </si>
+  <si>
+    <t>927307877834</t>
+  </si>
+  <si>
+    <t>927265307636</t>
+  </si>
+  <si>
+    <t>927275910385</t>
+  </si>
+  <si>
+    <t>927278980524</t>
+  </si>
+  <si>
+    <t>927292313218</t>
+  </si>
+  <si>
+    <t>927295311253</t>
+  </si>
+  <si>
+    <t>927301207021</t>
+  </si>
+  <si>
+    <t>927303799601</t>
+  </si>
+  <si>
+    <t>927308308138</t>
+  </si>
+  <si>
+    <t>928081258947</t>
+  </si>
+  <si>
+    <t>操作杆 9.43</t>
+  </si>
+  <si>
+    <t>928077558731</t>
+  </si>
+  <si>
+    <t>928067371935</t>
+  </si>
+  <si>
+    <t>928084824725</t>
+  </si>
+  <si>
+    <t>928518143633</t>
+  </si>
+  <si>
+    <t>928526186820</t>
+  </si>
+  <si>
+    <t>928544464310</t>
+  </si>
+  <si>
+    <t>928546966151</t>
+  </si>
+  <si>
+    <t>928081431091</t>
+  </si>
+  <si>
+    <t>928086982555</t>
+  </si>
+  <si>
+    <t>928002639195</t>
+  </si>
+  <si>
+    <t>我的世界狐狸 9.93</t>
+  </si>
+  <si>
+    <t>928005952331</t>
+  </si>
+  <si>
+    <t>928006463351</t>
+  </si>
+  <si>
+    <t>928081576387</t>
+  </si>
+  <si>
+    <t>928074110146</t>
+  </si>
+  <si>
+    <t>928066358995</t>
+  </si>
+  <si>
+    <t>928085245011</t>
+  </si>
+  <si>
+    <t>928547060593</t>
+  </si>
+  <si>
+    <t>928543752499</t>
+  </si>
+  <si>
+    <t>928525968107</t>
+  </si>
+  <si>
+    <t>928518630333</t>
+  </si>
+  <si>
+    <t>928562783666</t>
+  </si>
+  <si>
+    <t>我的世界小鸡3cm 6.15</t>
+  </si>
+  <si>
+    <t>928563155532</t>
+  </si>
+  <si>
+    <t>928563676874</t>
+  </si>
+  <si>
+    <t>928563843608</t>
+  </si>
+  <si>
+    <t>928659873048</t>
+  </si>
+  <si>
+    <t>928659789233</t>
+  </si>
+  <si>
+    <t>928659730962</t>
+  </si>
+  <si>
+    <t>928659576603</t>
+  </si>
+  <si>
+    <t>928527792933</t>
+  </si>
+  <si>
+    <t>928529280104</t>
+  </si>
+  <si>
+    <t>928529701312</t>
+  </si>
+  <si>
+    <t>928563321059</t>
+  </si>
+  <si>
+    <t>怪奇物语指尖陀螺 6.4</t>
+  </si>
+  <si>
+    <t>928563308426</t>
+  </si>
+  <si>
+    <t>928563201216</t>
+  </si>
+  <si>
+    <t>928562828638</t>
+  </si>
+  <si>
+    <t>928586440014</t>
+  </si>
+  <si>
+    <t>928586215087</t>
+  </si>
+  <si>
+    <t>928586155656</t>
+  </si>
+  <si>
+    <t>928586012344</t>
+  </si>
+  <si>
+    <t>928530728664</t>
+  </si>
+  <si>
+    <t>928531644425</t>
+  </si>
+  <si>
+    <t>928532159853</t>
+  </si>
+  <si>
+    <t>928586298856</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件站立 5.52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件傻站 5.41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起2 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线 5.38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线2 5.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带 5.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带2 5.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件8件套 18.84</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件4件套(站立、抓起、数据线、传送带) 11.28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件4件套2(傻站、抓起2、数据线2、传送带2) 11.18</t>
+    </r>
+  </si>
+  <si>
+    <t>928586120261</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件站立 5.52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件傻站 5.41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起2 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线 5.38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线2 5.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带 5.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带2 5.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件4件套(站立、抓起、数据线、传送带) 11.28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件4件套2(傻站、抓起2、数据线2、传送带2) 11.18</t>
+    </r>
+  </si>
+  <si>
+    <t>928585978364</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件站立 5.52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件傻站 5.41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起2 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线 5.38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线2 5.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带 5.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带2 5.54</t>
+    </r>
+  </si>
+  <si>
+    <t>928660146605</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件站立 5.52</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件傻站 5.41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件抓起2 5.67</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线 5.38</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件数据线2 5.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带 5.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件传送带2 5.54</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初音未来挂件8件套 18.84</t>
+    </r>
+  </si>
+  <si>
+    <t>928659826355</t>
+  </si>
+  <si>
+    <t>928659718970</t>
+  </si>
+  <si>
+    <t>928569221852</t>
+  </si>
+  <si>
+    <t>928575263831</t>
+  </si>
+  <si>
+    <t>928577285395</t>
+  </si>
+  <si>
+    <t>928585978593</t>
+  </si>
+  <si>
+    <t>初音未来挂件8件套 18.84</t>
+  </si>
+  <si>
+    <t>928659968321</t>
+  </si>
+  <si>
+    <t>929829385216</t>
+  </si>
+  <si>
+    <t>挽救计划氙岩小人6cm 5.15</t>
+  </si>
+  <si>
+    <t>929822935150</t>
+  </si>
+  <si>
+    <t>929790519843</t>
+  </si>
+  <si>
+    <t>929790316854</t>
+  </si>
+  <si>
+    <t>929790105543</t>
+  </si>
+  <si>
+    <t>929178306985</t>
+  </si>
+  <si>
+    <t>929831241006</t>
+  </si>
+  <si>
+    <t>929829281421</t>
+  </si>
+  <si>
+    <t>929790354582</t>
+  </si>
+  <si>
+    <t>929789853364</t>
+  </si>
+  <si>
+    <t>929789797423</t>
+  </si>
+  <si>
+    <t>929179975663</t>
+  </si>
+  <si>
+    <t>928768183935</t>
+  </si>
+  <si>
+    <t>928770763226</t>
+  </si>
+  <si>
+    <t>929818373015</t>
+  </si>
+  <si>
+    <t>930510716613</t>
+  </si>
+  <si>
+    <t>930514450365</t>
+  </si>
+  <si>
+    <t>930515084436</t>
+  </si>
+  <si>
+    <t>931294144251</t>
+  </si>
+  <si>
+    <t>931296526959</t>
+  </si>
+  <si>
+    <t>929857804903</t>
+  </si>
+  <si>
+    <t>三角洲三角币哈夫币(20个带盒子) 7.53</t>
+  </si>
+  <si>
+    <t>929897006895</t>
+  </si>
+  <si>
+    <t>929907123954</t>
+  </si>
+  <si>
+    <t>929824299843</t>
+  </si>
+  <si>
+    <t>929825493818</t>
+  </si>
+  <si>
+    <t>929828511673</t>
+  </si>
+  <si>
+    <t>929826422027</t>
+  </si>
+  <si>
+    <t>929816776572</t>
+  </si>
+  <si>
+    <t>929818123630</t>
+  </si>
+  <si>
+    <t>929811550506</t>
+  </si>
+  <si>
+    <t>929817616022</t>
+  </si>
+  <si>
+    <t>929970366534</t>
+  </si>
+  <si>
+    <t>趴玻璃的胖丁 9.08</t>
+  </si>
+  <si>
+    <t>929986839211</t>
+  </si>
+  <si>
+    <t>930003922542</t>
+  </si>
+  <si>
+    <t>930005637010</t>
+  </si>
+  <si>
+    <t>930012472638</t>
+  </si>
+  <si>
+    <t>930010923125</t>
+  </si>
+  <si>
+    <t>930007653608</t>
+  </si>
+  <si>
+    <t>930006291363</t>
+  </si>
+  <si>
+    <t>930008796476</t>
+  </si>
+  <si>
+    <t>930010351737</t>
+  </si>
+  <si>
+    <t>930006372464</t>
+  </si>
+  <si>
+    <t>大嘴花骷髅钥匙扣 4.81</t>
+  </si>
+  <si>
+    <t>930009586525</t>
+  </si>
+  <si>
+    <t>930011670053</t>
+  </si>
+  <si>
+    <t>930012803051</t>
+  </si>
+  <si>
+    <t>930004513316</t>
+  </si>
+  <si>
+    <t>930003020365</t>
+  </si>
+  <si>
+    <t>929999604616</t>
+  </si>
+  <si>
+    <t>929969968960</t>
+  </si>
+  <si>
+    <t>930006771512</t>
+  </si>
+  <si>
+    <t>930007502965</t>
+  </si>
+  <si>
+    <t>930008741294</t>
+  </si>
+  <si>
+    <t>930711856666</t>
+  </si>
+  <si>
+    <t>解压高压锅按键 6.38</t>
+  </si>
+  <si>
+    <t>930708323168</t>
+  </si>
+  <si>
+    <t>930706954238</t>
+  </si>
+  <si>
+    <t>930690395889</t>
+  </si>
+  <si>
+    <t>930711976641</t>
+  </si>
+  <si>
+    <t>930710982241</t>
+  </si>
+  <si>
+    <t>930707881251</t>
+  </si>
+  <si>
+    <t>930691553238</t>
+  </si>
+  <si>
+    <t>930726161330</t>
+  </si>
+  <si>
+    <t>撒出的饮料杯 21.46</t>
+  </si>
+  <si>
+    <t>930721244569</t>
+  </si>
+  <si>
+    <t>930719679443</t>
+  </si>
+  <si>
+    <t>930712992766</t>
+  </si>
+  <si>
+    <t>930726292523</t>
+  </si>
+  <si>
+    <t>930721548825</t>
+  </si>
+  <si>
+    <t>930718931400</t>
+  </si>
+  <si>
+    <t>930713488501</t>
+  </si>
+  <si>
+    <t>930736921057</t>
+  </si>
+  <si>
+    <t>生化危机9安魂曲里昂战斧36cm 25.74</t>
+  </si>
+  <si>
+    <t>930733721121</t>
+  </si>
+  <si>
+    <t>930731813253</t>
+  </si>
+  <si>
+    <t>930729256020</t>
+  </si>
+  <si>
+    <t>930728841795</t>
+  </si>
+  <si>
+    <t>930731506571</t>
+  </si>
+  <si>
+    <t>930735693062</t>
+  </si>
+  <si>
+    <t>930737076597</t>
+  </si>
+  <si>
+    <t>931288897331</t>
+  </si>
+  <si>
+    <t>装甲恐龙 6.66</t>
+  </si>
+  <si>
+    <t>931285473759</t>
+  </si>
+  <si>
+    <t>931278479329</t>
+  </si>
+  <si>
+    <t>931269904211</t>
+  </si>
+  <si>
+    <t>931290241347</t>
+  </si>
+  <si>
+    <t>931286815308</t>
+  </si>
+  <si>
+    <t>931278348250</t>
+  </si>
+  <si>
+    <t>931269514079</t>
+  </si>
+  <si>
+    <t>931953646251</t>
+  </si>
+  <si>
+    <t>编织解压龙蛋 13.7</t>
+  </si>
+  <si>
+    <t>931951781229</t>
+  </si>
+  <si>
+    <t>931948765762</t>
+  </si>
+  <si>
+    <t>931931839435</t>
+  </si>
+  <si>
+    <t>931953493436</t>
+  </si>
+  <si>
+    <t>931952828908</t>
+  </si>
+  <si>
+    <t>931949239286</t>
+  </si>
+  <si>
+    <t>931931365505</t>
+  </si>
+  <si>
+    <t>931968348603</t>
+  </si>
+  <si>
+    <t>2026世界杯奖杯模型10cm 7.6</t>
+  </si>
+  <si>
+    <t>931967261472</t>
+  </si>
+  <si>
+    <t>931963824056</t>
+  </si>
+  <si>
+    <t>931958392235</t>
+  </si>
+  <si>
+    <t>931970067680</t>
+  </si>
+  <si>
+    <t>931967604144</t>
+  </si>
+  <si>
+    <t>931965747230</t>
+  </si>
+  <si>
+    <t>931958226024</t>
+  </si>
+  <si>
+    <t>932402774530</t>
+  </si>
+  <si>
+    <t>鬼灭之刃徽章 8.54</t>
+  </si>
+  <si>
+    <t>932401064011</t>
+  </si>
+  <si>
+    <t>932397972764</t>
+  </si>
+  <si>
+    <t>932389371669</t>
+  </si>
+  <si>
+    <t>932388908143</t>
+  </si>
+  <si>
+    <t>932399499839</t>
+  </si>
+  <si>
+    <t>932400554681</t>
+  </si>
+  <si>
+    <t>932403294739</t>
+  </si>
+  <si>
+    <t>932517961879</t>
+  </si>
+  <si>
+    <t>平衡球 8.76</t>
+  </si>
+  <si>
+    <t>932515423380</t>
+  </si>
+  <si>
+    <t>932510558949</t>
+  </si>
+  <si>
+    <t>932464403445</t>
+  </si>
+  <si>
+    <t>932521421065</t>
+  </si>
+  <si>
+    <t>932519998395</t>
   </si>
 </sst>
 </file>
@@ -942,13 +4123,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1415,16 +4602,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1433,126 +4617,132 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2080,7 +5270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B190"/>
+  <dimension ref="A1:B500"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
@@ -2089,1524 +5279,3980 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="40.5" spans="1:2">
+    <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="40.5" spans="1:2">
+    <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:2">
+    <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" ht="27" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" ht="27" spans="1:2">
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" ht="27" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="27" spans="1:2">
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" ht="27" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="27" spans="1:2">
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" ht="27" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" ht="27" spans="1:2">
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" ht="27" spans="1:2">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" ht="27" spans="1:2">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" ht="27" spans="1:2">
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" ht="27" spans="1:2">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" ht="27" spans="1:2">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" ht="27" spans="1:2">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" ht="27" spans="1:2">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" ht="27" spans="1:2">
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" ht="27" spans="1:2">
+      <c r="B20" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" ht="27" spans="1:2">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" ht="27" spans="1:2">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" ht="27" spans="1:2">
-      <c r="A24" s="2" t="s">
+    <row r="25" spans="1:2">
+      <c r="A25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" ht="27" spans="1:2">
-      <c r="A25" s="2" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" ht="27" spans="1:2">
-      <c r="A26" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" ht="27" spans="1:2">
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" ht="27" spans="1:2">
-      <c r="A28" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" ht="27" spans="1:2">
-      <c r="A29" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" ht="27" spans="1:2">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:2">
+      <c r="A31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="31" ht="27" spans="1:2">
-      <c r="A31" s="2" t="s">
+    <row r="32" spans="1:2">
+      <c r="A32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" ht="27" spans="1:2">
-      <c r="A32" s="2" t="s">
+    <row r="33" spans="1:2">
+      <c r="A33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="33" ht="40.5" spans="1:2">
-      <c r="A33" s="2" t="s">
+    <row r="34" spans="1:2">
+      <c r="A34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="40.5" spans="1:2">
-      <c r="A34" s="2" t="s">
+    <row r="35" spans="1:2">
+      <c r="A35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" ht="27" spans="1:2">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:2">
+      <c r="A36" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36" ht="27" spans="1:2">
-      <c r="A36" s="2" t="s">
+    <row r="37" spans="1:2">
+      <c r="A37" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="37" ht="27" spans="1:2">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:2">
+      <c r="A38" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" ht="27" spans="1:2">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" ht="27" spans="1:2">
-      <c r="A39" s="2" t="s">
+    <row r="40" spans="1:2">
+      <c r="A40" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="40" ht="27" spans="1:2">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:2">
+      <c r="A41" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="41" ht="27" spans="1:2">
-      <c r="A41" s="2" t="s">
+    <row r="42" spans="1:2">
+      <c r="A42" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="42" ht="27" spans="1:2">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:2">
+      <c r="A43" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="43" ht="27" spans="1:2">
-      <c r="A43" s="2" t="s">
+    <row r="44" spans="1:2">
+      <c r="A44" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" ht="27" spans="1:2">
-      <c r="A44" s="2" t="s">
+    <row r="45" spans="1:2">
+      <c r="A45" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" ht="27" spans="1:2">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:2">
+      <c r="A46" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" ht="27" spans="1:2">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:2">
+      <c r="A47" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="47" ht="27" spans="1:2">
-      <c r="A47" s="2" t="s">
+    <row r="48" spans="1:2">
+      <c r="A48" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" ht="27" spans="1:2">
-      <c r="A48" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B48" s="1" t="s">
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="49" ht="27" spans="1:2">
-      <c r="A49" s="2" t="s">
+      <c r="B49" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="50" ht="27" spans="1:2">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B51" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="51" ht="27" spans="1:2">
-      <c r="A51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="52" ht="27" spans="1:2">
-      <c r="A52" s="2" t="s">
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B53" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="53" ht="27" spans="1:2">
-      <c r="A53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" ht="27" spans="1:2">
-      <c r="A54" s="2" t="s">
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B55" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="55" ht="27" spans="1:2">
-      <c r="A55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="56" ht="27" spans="1:2">
-      <c r="A56" s="2" t="s">
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="57" ht="27" spans="1:2">
-      <c r="A57" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="58" ht="27" spans="1:2">
-      <c r="A58" s="2" t="s">
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B59" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="59" ht="27" spans="1:2">
-      <c r="A59" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="60" ht="54" spans="1:2">
-      <c r="A60" s="2" t="s">
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B61" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="61" ht="54" spans="1:2">
-      <c r="A61" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="62" ht="54" spans="1:2">
-      <c r="A62" s="2" t="s">
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="63" ht="27" spans="1:2">
-      <c r="A63" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="64" ht="27" spans="1:2">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:2">
+      <c r="A65" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="65" ht="27" spans="1:2">
-      <c r="A65" s="2" t="s">
+    <row r="66" spans="1:2">
+      <c r="A66" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B66" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="66" ht="27" spans="1:2">
-      <c r="A66" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="67" ht="27" spans="1:2">
-      <c r="A67" s="2" t="s">
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B68" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="68" ht="27" spans="1:2">
-      <c r="A68" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" ht="27" spans="1:2">
-      <c r="A69" s="2" t="s">
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B70" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="70" ht="27" spans="1:2">
-      <c r="A70" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="71" ht="27" spans="1:2">
-      <c r="A71" s="2" t="s">
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B72" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="72" ht="27" spans="1:2">
-      <c r="A72" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="73" ht="108" spans="1:2">
-      <c r="A73" s="2" t="s">
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B74" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="74" ht="108" spans="1:2">
-      <c r="A74" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="75" ht="27" spans="1:2">
-      <c r="A75" s="2" t="s">
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B76" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="76" ht="27" spans="1:2">
-      <c r="A76" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="77" ht="27" spans="1:2">
-      <c r="A77" s="2" t="s">
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B78" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="78" ht="27" spans="1:2">
-      <c r="A78" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="79" ht="27" spans="1:2">
-      <c r="A79" s="2" t="s">
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B80" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="80" ht="27" spans="1:2">
-      <c r="A80" s="2" t="s">
+      <c r="B81" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="81" ht="27" spans="1:2">
-      <c r="A81" s="2" t="s">
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="82" ht="27" spans="1:2">
-      <c r="A82" s="2" t="s">
+      <c r="B82" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="83" ht="27" spans="1:2">
-      <c r="A83" s="2" t="s">
+      <c r="B83" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="84" ht="121.5" spans="1:2">
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="85" ht="121.5" spans="1:2">
-      <c r="A85" s="2" t="s">
+      <c r="B85" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="86" ht="27" spans="1:2">
-      <c r="A86" s="2" t="s">
+      <c r="B86" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B87" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="87" ht="27" spans="1:2">
-      <c r="A87" s="2" t="s">
+      <c r="B88" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="88" ht="27" spans="1:2">
-      <c r="A88" s="2" t="s">
+      <c r="B89" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="89" ht="27" spans="1:2">
-      <c r="A89" s="2" t="s">
+      <c r="B90" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B91" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="90" ht="27" spans="1:2">
-      <c r="A90" s="2" t="s">
+      <c r="B92" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="91" ht="27" spans="1:2">
-      <c r="A91" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B91" s="1" t="s">
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="92" ht="27" spans="1:2">
-      <c r="A92" s="2" t="s">
+      <c r="B94" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B95" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="93" ht="27" spans="1:2">
-      <c r="A93" s="2" t="s">
+    <row r="96" spans="1:2">
+      <c r="A96" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B96" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="94" ht="27" spans="1:2">
-      <c r="A94" s="2" t="s">
+    <row r="97" spans="1:2">
+      <c r="A97" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B97" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="95" ht="27" spans="1:2">
-      <c r="A95" s="2" t="s">
+      <c r="B98" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="96" ht="27" spans="1:2">
-      <c r="A96" s="2" t="s">
+      <c r="B99" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B100" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="97" ht="27" spans="1:2">
-      <c r="A97" s="2" t="s">
+      <c r="B101" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="98" ht="27" spans="1:2">
-      <c r="A98" s="2" t="s">
+      <c r="B102" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B103" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="99" ht="27" spans="1:2">
-      <c r="A99" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="100" ht="27" spans="1:2">
-      <c r="A100" s="2" t="s">
+      <c r="B105" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B106" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="101" ht="27" spans="1:2">
-      <c r="A101" s="2" t="s">
+      <c r="B107" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="102" ht="27" spans="1:2">
-      <c r="A102" s="2" t="s">
+      <c r="B108" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B109" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="103" ht="27" spans="1:2">
-      <c r="A103" s="2" t="s">
+    <row r="110" spans="1:2">
+      <c r="A110" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B110" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="104" ht="27" spans="1:2">
-      <c r="A104" s="2" t="s">
+    <row r="111" spans="1:2">
+      <c r="A111" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="105" ht="27" spans="1:2">
-      <c r="A105" s="2" t="s">
+      <c r="B111" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="106" ht="27" spans="1:2">
-      <c r="A106" s="2" t="s">
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="107" ht="27" spans="1:2">
-      <c r="A107" s="2" t="s">
+      <c r="B112" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B113" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="108" ht="27" spans="1:2">
-      <c r="A108" s="2" t="s">
+      <c r="B114" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="109" ht="40.5" spans="1:2">
-      <c r="A109" s="2" t="s">
+      <c r="B115" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="B116" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="110" ht="40.5" spans="1:2">
-      <c r="A110" s="2" t="s">
+      <c r="B117" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="111" ht="40.5" spans="1:2">
-      <c r="A111" s="2" t="s">
+      <c r="B118" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="112" ht="27" spans="1:2">
-      <c r="A112" s="2" t="s">
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B119" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="113" ht="27" spans="1:2">
-      <c r="A113" s="2" t="s">
+      <c r="B120" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="114" ht="27" spans="1:2">
-      <c r="A114" s="2" t="s">
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B121" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="115" ht="27" spans="1:2">
-      <c r="A115" s="2" t="s">
+      <c r="B122" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="116" ht="27" spans="1:2">
-      <c r="A116" s="2" t="s">
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="117" ht="27" spans="1:2">
-      <c r="A117" s="2" t="s">
+      <c r="B123" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B124" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="118" ht="27" spans="1:2">
-      <c r="A118" s="2" t="s">
+    <row r="125" spans="1:2">
+      <c r="A125" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B125" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="119" ht="27" spans="1:2">
-      <c r="A119" s="2" t="s">
+    <row r="126" spans="1:2">
+      <c r="A126" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B126" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="120" ht="27" spans="1:2">
-      <c r="A120" s="2" t="s">
+    <row r="127" spans="1:2">
+      <c r="A127" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B127" s="2" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="121" ht="27" spans="1:2">
-      <c r="A121" s="2" t="s">
+    <row r="128" spans="1:2">
+      <c r="A128" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="122" ht="27" spans="1:2">
-      <c r="A122" s="2" t="s">
+      <c r="B128" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B122" s="1" t="s">
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="123" ht="27" spans="1:2">
-      <c r="A123" s="2" t="s">
+      <c r="B129" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="124" ht="27" spans="1:2">
-      <c r="A124" s="2" t="s">
+      <c r="B130" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B131" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="125" ht="27" spans="1:2">
-      <c r="A125" s="2" t="s">
+      <c r="B132" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="126" ht="27" spans="1:2">
-      <c r="A126" s="2" t="s">
+      <c r="B133" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B126" s="1" t="s">
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="127" ht="27" spans="1:2">
-      <c r="A127" s="2" t="s">
+      <c r="B134" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="128" ht="27" spans="1:2">
-      <c r="A128" s="2" t="s">
+      <c r="B135" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B128" s="1" t="s">
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="129" ht="27" spans="1:2">
-      <c r="A129" s="2" t="s">
+      <c r="B136" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="130" ht="67.5" spans="1:2">
-      <c r="A130" s="2" t="s">
+      <c r="B137" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B138" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="131" ht="27" spans="1:2">
-      <c r="A131" s="2" t="s">
+    <row r="139" spans="1:2">
+      <c r="A139" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B139" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="132" ht="94.5" spans="1:2">
-      <c r="A132" s="2" t="s">
+      <c r="B140" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B132" s="1" t="s">
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="133" ht="94.5" spans="1:2">
-      <c r="A133" s="2" t="s">
+      <c r="B141" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="134" ht="27" spans="1:2">
-      <c r="A134" s="2" t="s">
+      <c r="B142" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B143" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="135" ht="27" spans="1:2">
-      <c r="A135" s="2" t="s">
+      <c r="B144" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="B145" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="136" ht="94.5" spans="1:2">
-      <c r="A136" s="2" t="s">
+      <c r="B146" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B136" s="1" t="s">
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="137" ht="94.5" spans="1:2">
-      <c r="A137" s="2" t="s">
+      <c r="B147" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="138" ht="94.5" spans="1:2">
-      <c r="A138" s="2" t="s">
+      <c r="B148" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="139" ht="27" spans="1:2">
-      <c r="A139" s="2" t="s">
+      <c r="B149" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B150" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="140" ht="27" spans="1:2">
-      <c r="A140" s="2" t="s">
+      <c r="B151" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="141" ht="27" spans="1:2">
-      <c r="A141" s="2" t="s">
+      <c r="B152" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B141" s="1" t="s">
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="142" ht="27" spans="1:2">
-      <c r="A142" s="2" t="s">
+      <c r="B153" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="143" ht="27" spans="1:2">
-      <c r="A143" s="2" t="s">
+      <c r="B154" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="144" ht="27" spans="1:2">
-      <c r="A144" s="2" t="s">
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="B155" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="145" ht="27" spans="1:2">
-      <c r="A145" s="2" t="s">
+      <c r="B156" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="146" ht="27" spans="1:2">
-      <c r="A146" s="2" t="s">
+      <c r="B157" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B146" s="1" t="s">
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="147" ht="27" spans="1:2">
-      <c r="A147" s="2" t="s">
+      <c r="B158" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="148" ht="27" spans="1:2">
-      <c r="A148" s="2" t="s">
+      <c r="B159" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="B160" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="149" ht="27" spans="1:2">
-      <c r="A149" s="2" t="s">
+      <c r="B161" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B149" s="1" t="s">
+      <c r="B162" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="150" ht="27" spans="1:2">
-      <c r="A150" s="2" t="s">
+    <row r="163" spans="1:2">
+      <c r="A163" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="B163" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="151" ht="27" spans="1:2">
-      <c r="A151" s="2" t="s">
+    <row r="164" spans="1:2">
+      <c r="A164" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B164" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="152" ht="27" spans="1:2">
-      <c r="A152" s="2" t="s">
+    <row r="165" spans="1:2">
+      <c r="A165" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="B165" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="153" ht="27" spans="1:2">
-      <c r="A153" s="2" t="s">
+    <row r="166" spans="1:2">
+      <c r="A166" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B166" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="154" ht="27" spans="1:2">
-      <c r="A154" s="2" t="s">
+      <c r="B167" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="155" ht="27" spans="1:2">
-      <c r="A155" s="2" t="s">
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B168" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="156" ht="27" spans="1:2">
-      <c r="A156" s="2" t="s">
+      <c r="B169" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="157" ht="27" spans="1:2">
-      <c r="A157" s="2" t="s">
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B170" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="158" ht="27" spans="1:2">
-      <c r="A158" s="2" t="s">
+      <c r="B171" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="159" ht="27" spans="1:2">
-      <c r="A159" s="2" t="s">
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="160" ht="27" spans="1:2">
-      <c r="A160" s="2" t="s">
+      <c r="B172" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B173" s="2" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="161" ht="27" spans="1:2">
-      <c r="A161" s="2" t="s">
+    <row r="174" spans="1:2">
+      <c r="A174" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="162" ht="27" spans="1:2">
-      <c r="A162" s="2" t="s">
+      <c r="B174" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="B162" s="1" t="s">
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="163" ht="27" spans="1:2">
-      <c r="A163" s="2" t="s">
+      <c r="B175" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="164" ht="27" spans="1:2">
-      <c r="A164" s="2" t="s">
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B176" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="165" ht="27" spans="1:2">
-      <c r="A165" s="2" t="s">
+      <c r="B177" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="B178" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="166" ht="27" spans="1:2">
-      <c r="A166" s="2" t="s">
+    <row r="179" spans="1:2">
+      <c r="A179" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B179" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="167" ht="27" spans="1:2">
-      <c r="A167" s="2" t="s">
+      <c r="B180" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B167" s="1" t="s">
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="168" ht="27" spans="1:2">
-      <c r="A168" s="2" t="s">
+      <c r="B181" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="169" ht="27" spans="1:2">
-      <c r="A169" s="2" t="s">
+      <c r="B182" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="170" ht="27" spans="1:2">
-      <c r="A170" s="2" t="s">
+      <c r="B183" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B184" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="171" ht="27" spans="1:2">
-      <c r="A171" s="2" t="s">
+      <c r="B185" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="172" ht="27" spans="1:2">
-      <c r="A172" s="2" t="s">
+      <c r="B186" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B172" s="1" t="s">
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="173" ht="27" spans="1:2">
-      <c r="A173" s="2" t="s">
+      <c r="B187" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="174" ht="27" spans="1:2">
-      <c r="A174" s="2" t="s">
+      <c r="B188" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B174" s="1" t="s">
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="175" ht="67.5" spans="1:2">
-      <c r="A175" s="2" t="s">
+      <c r="B189" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="B190" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="176" ht="27" spans="1:2">
-      <c r="A176" s="2" t="s">
+    <row r="191" spans="1:2">
+      <c r="A191" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="B191" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="177" ht="27" spans="1:2">
-      <c r="A177" s="2" t="s">
+    <row r="192" spans="1:2">
+      <c r="A192" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B192" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="178" ht="27" spans="1:2">
-      <c r="A178" s="2" t="s">
+    <row r="193" spans="1:2">
+      <c r="A193" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="B193" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="179" ht="27" spans="1:2">
-      <c r="A179" s="2" t="s">
+    <row r="194" spans="1:2">
+      <c r="A194" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="B194" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="180" ht="27" spans="1:2">
-      <c r="A180" s="2" t="s">
+    <row r="195" spans="1:2">
+      <c r="A195" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="B195" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="181" ht="27" spans="1:2">
-      <c r="A181" s="2" t="s">
+    <row r="196" spans="1:2">
+      <c r="A196" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="B196" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="182" ht="27" spans="1:2">
-      <c r="A182" s="2" t="s">
+      <c r="B197" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="183" ht="27" spans="1:2">
-      <c r="A183" s="2" t="s">
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="B198" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="184" ht="27" spans="1:2">
-      <c r="A184" s="2" t="s">
+      <c r="B199" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="185" ht="27" spans="1:2">
-      <c r="A185" s="2" t="s">
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="B200" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="186" ht="27" spans="1:2">
-      <c r="A186" s="2" t="s">
+      <c r="B201" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="187" ht="27" spans="1:2">
-      <c r="A187" s="2" t="s">
+      <c r="B202" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B187" s="1" t="s">
+      <c r="B203" s="2" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="188" ht="27" spans="1:2">
-      <c r="A188" s="2" t="s">
+    <row r="204" spans="1:2">
+      <c r="A204" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="B204" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="189" ht="27" spans="1:2">
-      <c r="A189" s="2" t="s">
+      <c r="B205" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B189" s="1" t="s">
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="190" ht="27" spans="1:2">
-      <c r="A190" s="2" t="s">
+      <c r="B206" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="B207" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B334" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B385" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B429" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B461" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B463" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="2"/>
+      <c r="B495" s="2"/>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="2"/>
+      <c r="B496" s="2"/>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="3"/>
+      <c r="B497" s="3"/>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="3"/>
+      <c r="B498" s="3"/>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="3"/>
+      <c r="B499" s="3"/>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="3"/>
+      <c r="B500" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
